--- a/outputs/milk/silpo/primary_chain_output.xlsx
+++ b/outputs/milk/silpo/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01248306245783195</v>
+        <v>0.01248306245784421</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>4.729732285866721e-13</v>
+        <v>4.729732285868142e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.068911264269411e-21</v>
+        <v>1.068911264269473e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.01</v>
       </c>
       <c r="D3" t="n">
-        <v>3.818978011570181e-13</v>
+        <v>3.818978011570844e-13</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4125656034645e-11</v>
+        <v>4.41256560346402e-11</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -624,13 +624,13 @@
         <v>0.02253830533462102</v>
       </c>
       <c r="D4" t="n">
-        <v>1.862588539502195e-08</v>
+        <v>1.862588539502213e-08</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007337482414083636</v>
+        <v>0.0007337482414083765</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.0747088730315122</v>
+        <v>0.07470887303151186</v>
       </c>
       <c r="N5" t="n">
         <v>201</v>
@@ -942,10 +942,10 @@
         <v>201</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6442401315402562</v>
+        <v>0.6442401315402435</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2843166259159834</v>
+        <v>-0.2843166259159418</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -1016,16 +1016,16 @@
         <v>197</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002155003969288638</v>
+        <v>-0.002155003969288249</v>
       </c>
       <c r="K3" t="n">
         <v>-0.3006834081052232</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9538372381620318</v>
+        <v>-0.9538372381620321</v>
       </c>
       <c r="M3" t="n">
-        <v>3.295228800215539e-21</v>
+        <v>3.295228800215894e-21</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -1094,22 +1094,22 @@
         <v>199</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0146434053790121</v>
+        <v>0.01464340537901077</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7451033547254826</v>
+        <v>-0.7451033547254802</v>
       </c>
       <c r="L4" t="n">
         <v>-1.091145579024727</v>
       </c>
       <c r="M4" t="n">
-        <v>2.210764505250913e-26</v>
+        <v>2.210764505227035e-26</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9865928543793412</v>
+        <v>0.9865928543792826</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01665697627998265</v>
+        <v>0.016656976279983</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
@@ -1176,16 +1176,16 @@
         <v>35</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03780420860354025</v>
+        <v>0.0378042086035402</v>
       </c>
       <c r="K5" t="n">
         <v>0.07959450904544814</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9002155090608189</v>
+        <v>-0.9002155090608192</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0004638981008127622</v>
+        <v>0.0004638981008127678</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1254,22 +1254,22 @@
         <v>35</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1309588230301683</v>
+        <v>0.1309588230301686</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1145390198263037</v>
+        <v>0.1145390198263035</v>
       </c>
       <c r="L6" t="n">
         <v>-1.148712470677768</v>
       </c>
       <c r="M6" t="n">
-        <v>2.159825703867926e-05</v>
+        <v>2.159825703741887e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1648589481018799</v>
+        <v>0.1648589481018581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3223870280245842</v>
+        <v>0.3223870280245963</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9979470328795065</v>
+        <v>0.997947032879507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2079845355603383</v>
+        <v>0.2079845355601896</v>
       </c>
       <c r="G2" t="n">
-        <v>2.474090685541242e-48</v>
+        <v>2.474090685540177e-48</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.153692432382161</v>
+        <v>0.1536924323821612</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00213984567239458</v>
+        <v>0.002139845672394596</v>
       </c>
       <c r="G3" t="n">
-        <v>4.744864281636172e-221</v>
+        <v>4.744864281639144e-221</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1477169652972014</v>
+        <v>0.1477169652972021</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004696321631414695</v>
+        <v>0.0004696321631414275</v>
       </c>
       <c r="G4" t="n">
-        <v>8.675957601558099e-203</v>
+        <v>8.675957601562549e-203</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9838835608618119</v>
+        <v>0.9838835608618121</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7600112143069815</v>
+        <v>0.7600112143069808</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04648178311126343</v>
+        <v>0.04648178311126383</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9821137350650249</v>
+        <v>0.9821137350650245</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7475783559300608</v>
+        <v>0.7475783559300255</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1112173090340839</v>
+        <v>0.1112173090340909</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -57549,7 +57549,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.774293874103992</v>
+        <v>-1.774293874103995</v>
       </c>
       <c r="C2" t="n">
         <v>-1.788937279483005</v>
@@ -57565,10 +57565,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.896552577620362</v>
+        <v>-1.896552577620365</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.912204994969054</v>
+        <v>-1.912204994969057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57581,10 +57581,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.904976881397576</v>
+        <v>-1.90497688139758</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.920698825275694</v>
+        <v>-1.920698825275696</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57597,10 +57597,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.905557362721929</v>
+        <v>-1.905557362721933</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.92128409736412</v>
+        <v>-1.921284097364122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57613,10 +57613,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.90559736110955</v>
+        <v>-1.905597361109554</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.921324425861997</v>
+        <v>-1.921324425861999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57629,10 +57629,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.905600117220635</v>
+        <v>-1.905600117220639</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.921327204719512</v>
+        <v>-1.921327204719514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57645,10 +57645,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.905600307131998</v>
+        <v>-1.905600307132002</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.92132739619823</v>
+        <v>-1.921327396198232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57661,10 +57661,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.905600320217945</v>
+        <v>-1.905600320217949</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.921327409392177</v>
+        <v>-1.92132740939218</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57677,10 +57677,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.90560032111964</v>
+        <v>-1.905600321119644</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.921327410301313</v>
+        <v>-1.921327410301316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57693,10 +57693,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.905600321181772</v>
+        <v>-1.905600321181776</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.921327410363958</v>
+        <v>-1.921327410363961</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57709,10 +57709,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.905600321186053</v>
+        <v>-1.905600321186057</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.921327410368274</v>
+        <v>-1.921327410368277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57725,10 +57725,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.905600321186348</v>
+        <v>-1.905600321186352</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.921327410368572</v>
+        <v>-1.921327410368574</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57741,10 +57741,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.905600321186368</v>
+        <v>-1.905600321186372</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.921327410368592</v>
+        <v>-1.921327410368595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57757,10 +57757,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57773,10 +57773,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57789,10 +57789,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57805,10 +57805,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57821,10 +57821,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57837,10 +57837,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57853,10 +57853,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57869,10 +57869,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.90560032118637</v>
+        <v>-1.905600321186374</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.921327410368594</v>
+        <v>-1.921327410368596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -57885,10 +57885,10 @@
         <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>0.06345346241198734</v>
+        <v>0.06345346241198797</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.06750536061818097</v>
+        <v>-0.06750536061818059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -57901,10 +57901,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06926473730126741</v>
+        <v>0.06926473730126805</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07368772155075193</v>
+        <v>-0.07368772155075146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -57917,10 +57917,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0697969527951913</v>
+        <v>0.06979695279519194</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.07425392231392933</v>
+        <v>-0.07425392231392884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -57933,10 +57933,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>0.06984569482467182</v>
+        <v>0.06984569482467244</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.07430577682512969</v>
+        <v>-0.07430577682512921</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -57949,10 +57949,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>0.06985015877858711</v>
+        <v>0.06985015877858773</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.07431052583026479</v>
+        <v>-0.0743105258302643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -57965,10 +57965,10 @@
         <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>0.06985056760203517</v>
+        <v>0.0698505676020358</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07431096075963259</v>
+        <v>-0.07431096075963209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -57981,10 +57981,10 @@
         <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>0.06985060504341895</v>
+        <v>0.06985060504341957</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.07431100059188156</v>
+        <v>-0.07431100059188107</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -57997,10 +57997,10 @@
         <v>7</v>
       </c>
       <c r="B30" t="n">
-        <v>0.06985060847242289</v>
+        <v>0.06985060847242353</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.07431100423984874</v>
+        <v>-0.07431100423984825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -58013,10 +58013,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>0.06985060878646225</v>
+        <v>0.06985060878646288</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.07431100457394146</v>
+        <v>-0.07431100457394098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -58029,10 +58029,10 @@
         <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>0.06985060881522299</v>
+        <v>0.06985060881522362</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07431100460453877</v>
+        <v>-0.07431100460453828</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -58045,10 +58045,10 @@
         <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>0.069850608817857</v>
+        <v>0.06985060881785762</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07431100460734097</v>
+        <v>-0.07431100460734048</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -58061,10 +58061,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="n">
-        <v>0.06985060881809824</v>
+        <v>0.06985060881809886</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0743110046075976</v>
+        <v>-0.07431100460759711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -58077,10 +58077,10 @@
         <v>12</v>
       </c>
       <c r="B35" t="n">
-        <v>0.06985060881812033</v>
+        <v>0.06985060881812095</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.07431100460762111</v>
+        <v>-0.07431100460762062</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -58093,10 +58093,10 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0.06985060881812234</v>
+        <v>0.06985060881812297</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.07431100460762326</v>
+        <v>-0.07431100460762277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -58109,10 +58109,10 @@
         <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0.06985060881812254</v>
+        <v>0.06985060881812316</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.07431100460762345</v>
+        <v>-0.07431100460762297</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -58125,10 +58125,10 @@
         <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -58141,10 +58141,10 @@
         <v>16</v>
       </c>
       <c r="B39" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -58157,10 +58157,10 @@
         <v>17</v>
       </c>
       <c r="B40" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -58173,10 +58173,10 @@
         <v>18</v>
       </c>
       <c r="B41" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -58189,10 +58189,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -58205,10 +58205,10 @@
         <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>0.06985060881812255</v>
+        <v>0.06985060881812317</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.07431100460762348</v>
+        <v>-0.07431100460762298</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
